--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975015A2-7892-4421-9F98-04B7E3964FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E8ED3F-5E42-4FFA-89D8-88C69DE3B150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="业务列表" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="239">
   <si>
     <t>委托日期</t>
   </si>
@@ -881,10 +881,6 @@
     <t>执行完毕</t>
   </si>
   <si>
-    <t>退回案件</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>移交法院排队立案</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -906,6 +902,41 @@
   </si>
   <si>
     <t>贷款种类</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>案件退回</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>批转</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF606266"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>已</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF606266"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>移交执行组</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行时效</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -913,7 +944,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1005,6 +1036,20 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF606266"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF606266"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1032,7 +1077,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1067,6 +1112,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1369,40 +1417,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DV3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:DW3"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="61.109375" customWidth="1"/>
+    <col min="4" max="4" width="61.08984375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" style="15" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" customWidth="1"/>
+    <col min="6" max="6" width="23.6328125" style="15" customWidth="1"/>
+    <col min="7" max="7" width="19.54296875" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="22.88671875" style="15" customWidth="1"/>
-    <col min="10" max="10" width="19.6640625" customWidth="1"/>
+    <col min="9" max="9" width="22.90625" style="15" customWidth="1"/>
+    <col min="10" max="10" width="19.6328125" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="22.33203125" style="15" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="22.36328125" style="15" customWidth="1"/>
+    <col min="13" max="13" width="19.08984375" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="23.44140625" style="15" customWidth="1"/>
-    <col min="16" max="16" width="19.77734375" customWidth="1"/>
+    <col min="15" max="15" width="23.453125" style="15" customWidth="1"/>
+    <col min="16" max="16" width="19.81640625" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="22.109375" style="15" customWidth="1"/>
-    <col min="19" max="19" width="19.77734375" customWidth="1"/>
+    <col min="18" max="18" width="22.08984375" style="15" customWidth="1"/>
+    <col min="19" max="19" width="19.81640625" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="22.6640625" style="15" customWidth="1"/>
-    <col min="22" max="22" width="20.33203125" customWidth="1"/>
+    <col min="21" max="21" width="22.6328125" style="15" customWidth="1"/>
+    <col min="22" max="22" width="20.36328125" customWidth="1"/>
     <col min="23" max="64" width="18" customWidth="1"/>
-    <col min="65" max="65" width="26.77734375" customWidth="1"/>
+    <col min="65" max="65" width="26.81640625" customWidth="1"/>
     <col min="66" max="67" width="18" customWidth="1"/>
-    <col min="68" max="68" width="21.21875" customWidth="1"/>
-    <col min="69" max="117" width="18" customWidth="1"/>
-    <col min="118" max="118" width="25.109375" customWidth="1"/>
-    <col min="119" max="125" width="18" customWidth="1"/>
-    <col min="126" max="126" width="23" customWidth="1"/>
+    <col min="68" max="68" width="21.1796875" customWidth="1"/>
+    <col min="69" max="118" width="18" customWidth="1"/>
+    <col min="119" max="119" width="25.08984375" customWidth="1"/>
+    <col min="120" max="126" width="18" customWidth="1"/>
+    <col min="127" max="127" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:126">
+    <row r="1" spans="1:127">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -1618,7 +1666,7 @@
         <v>39</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BV1" s="1" t="s">
         <v>40</v>
@@ -1669,118 +1717,121 @@
         <v>53</v>
       </c>
       <c r="CL1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="CM1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="DA1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="DI1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="DJ1" s="1" t="s">
+      <c r="DK1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="DK1" s="1" t="s">
+      <c r="DL1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="DL1" s="1" t="s">
+      <c r="DM1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="DM1" s="1" t="s">
+      <c r="DN1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="DN1" s="1" t="s">
+      <c r="DO1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="DO1" s="1" t="s">
+      <c r="DP1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="DP1" s="1" t="s">
+      <c r="DQ1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="DQ1" s="1" t="s">
+      <c r="DR1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="DR1" s="1" t="s">
+      <c r="DS1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="DS1" s="1" t="s">
+      <c r="DT1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="DT1" s="1" t="s">
+      <c r="DU1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="DU1" s="1" t="s">
+      <c r="DV1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="DV1" s="1" t="s">
+      <c r="DW1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:126">
+    <row r="2" spans="1:127">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -1915,31 +1966,32 @@
       <c r="DT2" s="2"/>
       <c r="DU2" s="2"/>
       <c r="DV2" s="2"/>
-    </row>
-    <row r="3" spans="1:126">
+      <c r="DW2" s="2"/>
+    </row>
+    <row r="3" spans="1:127">
       <c r="B3" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations xWindow="522" yWindow="377" count="8">
+  <dataValidations xWindow="522" yWindow="377" count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF1:AF1048576" xr:uid="{42D0D285-222E-4112-8984-9734F9F28D29}">
       <formula1>"一般代理,特别代理"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="AU1:AY1048576 CP1:CP1048576 CQ1:CQ1048576 CV1:CV1048576" xr:uid="{4464FD37-F9F7-4812-BDD0-74E3B51C122E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="AU1:AY1048576 CQ1:CQ1048576 CR1:CR1048576 CW1:CW1048576" xr:uid="{4464FD37-F9F7-4812-BDD0-74E3B51C122E}">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="CL1:CL1048576" xr:uid="{DF26E270-6DC0-4AFD-AA4B-27A7D308895F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="CM1:CM1048576" xr:uid="{DF26E270-6DC0-4AFD-AA4B-27A7D308895F}">
       <formula1>"判决,裁定,调解"</formula1>
     </dataValidation>
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="日期分隔符必须使用-或/进行分隔" sqref="B1:B1048576" xr:uid="{76EC1C81-A985-4B80-8417-4F39E45BF715}">
       <formula1>1</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="日期分隔符必须为-或/" sqref="AC1:AC1048576 AK1:AK1048576 AL1:AL1048576 AM1:AM1048576 AZ1:AZ1048576 BA1:BA1048576 BE1:BE1048576 BG1:BG1048576 BI1:BI1048576 BJ1:BJ1048576 BK1:BK1048576 BL1:BL1048576 BZ1:BZ1048576 CA1:CA1048576 CC1:CC1048576 CB1:CB1048576 CD1:CD1048576 CH1:CH1048576 CI1:CI1048576 CK1:CK1048576 CS1:CS1048576 CW1:CW1048576 CX1:CX1048576 DE1:DE1048576 DF1:DF1048576 DG1:DG1048576 DH1:DH1048576 DI1:DI1048576 DM1:DM1048576 DO1:DO1048576 DQ1:DQ1048576 DR1:DR1048576 DS1:DS1048576" xr:uid="{CA5C5D4D-7B3F-4AD6-8F9A-9FFBDB572669}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="日期分隔符必须为-或/" sqref="AC1:AC1048576 AK1:AK1048576 AL1:AL1048576 AM1:AM1048576 AZ1:AZ1048576 BA1:BA1048576 BE1:BE1048576 BG1:BG1048576 BI1:BI1048576 BJ1:BJ1048576 BK1:BK1048576 BL1:BL1048576 BZ1:BZ1048576 CA1:CA1048576 CC1:CC1048576 CB1:CB1048576 CD1:CD1048576 CH1:CH1048576 CI1:CI1048576 DT1:DT1048576 CT1:CT1048576 CX1:CX1048576 CY1:CY1048576 DF1:DF1048576 DG1:DG1048576 DH1:DH1048576 DI1:DI1048576 DJ1:DJ1048576 DN1:DN1048576 DP1:DP1048576 DR1:DR1048576 DS1:DS1048576 CK1:CK1048576" xr:uid="{CA5C5D4D-7B3F-4AD6-8F9A-9FFBDB572669}">
       <formula1>1</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="当前输入格式非纯数字格式" sqref="AB1:AB1048576 BF1:BF1048576 BH1:BH1048576 BW1:BW1048576 BX1:BX1048576 BY1:BY1048576 CN1:CN1048576 CO1:CO1048576 CY1:CY1048576 CZ1:CZ1048576 DK1:DK1048576 DT1:DT1048576" xr:uid="{2CD1D548-3868-45C8-A9C8-D03CD7D9AEAE}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="当前输入格式非纯数字格式" sqref="AB1:AB1048576 BF1:BF1048576 BH1:BH1048576 BW1:BW1048576 BX1:BX1048576 BY1:BY1048576 CO1:CO1048576 CP1:CP1048576 CZ1:CZ1048576 DA1:DA1048576 DL1:DL1048576 DU1:DU1048576" xr:uid="{2CD1D548-3868-45C8-A9C8-D03CD7D9AEAE}">
       <formula1>-9999999999</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
@@ -1947,6 +1999,10 @@
       <formula1>"个贷,房贷,信用卡,普惠"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="BU1:BU1048576" xr:uid="{9183054B-50BF-4B63-A679-9F570E167A4C}"/>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="日期分隔符必须为-或/" sqref="CL1:CL1048576" xr:uid="{8DE077BB-0DCC-4B34-8C4C-038ADE8176A0}">
+      <formula1>36161</formula1>
+      <formula2>401404</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
@@ -1984,7 +2040,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" xr:uid="{30DA0B9C-AA69-412C-966A-84DD4AAAAF56}">
           <x14:formula1>
-            <xm:f>下拉菜单!$E$1:$E$28</xm:f>
+            <xm:f>下拉菜单!$E$1:$E$30</xm:f>
           </x14:formula1>
           <xm:sqref>BO1:BO1048576</xm:sqref>
         </x14:dataValidation>
@@ -1997,14 +2053,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="27.77734375" style="15" customWidth="1"/>
+    <col min="5" max="5" width="27.81640625" style="15" customWidth="1"/>
     <col min="6" max="7" width="18" customWidth="1"/>
-    <col min="9" max="9" width="41.77734375" customWidth="1"/>
-    <col min="10" max="10" width="46.109375" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="41.81640625" customWidth="1"/>
+    <col min="10" max="10" width="46.08984375" customWidth="1"/>
+    <col min="11" max="11" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -2064,18 +2120,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{068C94DB-3A5F-4F6E-BA5A-436C41DCF235}">
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" customWidth="1"/>
-    <col min="5" max="5" width="24.88671875" customWidth="1"/>
-    <col min="6" max="6" width="33.21875" customWidth="1"/>
+    <col min="1" max="1" width="17.90625" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
+    <col min="3" max="3" width="16.90625" customWidth="1"/>
+    <col min="4" max="4" width="16.36328125" customWidth="1"/>
+    <col min="5" max="5" width="24.90625" customWidth="1"/>
+    <col min="6" max="6" width="33.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="14.5">
       <c r="A1" s="8" t="s">
         <v>139</v>
       </c>
@@ -2089,13 +2145,13 @@
         <v>165</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" ht="14.5">
       <c r="A2" s="8" t="s">
         <v>140</v>
       </c>
@@ -2109,13 +2165,13 @@
         <v>166</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="14.5">
       <c r="A3" s="8" t="s">
         <v>141</v>
       </c>
@@ -2129,13 +2185,13 @@
         <v>167</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="14.5">
       <c r="A4" s="8" t="s">
         <v>142</v>
       </c>
@@ -2149,13 +2205,13 @@
         <v>168</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" ht="14.5">
       <c r="A5" s="8" t="s">
         <v>143</v>
       </c>
@@ -2168,14 +2224,14 @@
       <c r="D5" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>194</v>
+      <c r="E5" s="11" t="s">
+        <v>229</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" ht="14.5">
       <c r="A6" s="8" t="s">
         <v>144</v>
       </c>
@@ -2189,13 +2245,13 @@
         <v>170</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" ht="14.5">
       <c r="A7" s="8" t="s">
         <v>145</v>
       </c>
@@ -2206,13 +2262,13 @@
         <v>192</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" ht="14.5">
       <c r="A8" s="8" t="s">
         <v>146</v>
       </c>
@@ -2223,27 +2279,27 @@
         <v>171</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" ht="14.5">
       <c r="A9" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>198</v>
+      <c r="E9" s="16" t="s">
+        <v>237</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" ht="14.5">
       <c r="A10" s="9" t="s">
         <v>148</v>
       </c>
@@ -2251,13 +2307,13 @@
         <v>173</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" ht="14.5">
       <c r="A11" s="9" t="s">
         <v>149</v>
       </c>
@@ -2265,13 +2321,13 @@
         <v>174</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" ht="14.5">
       <c r="A12" s="9" t="s">
         <v>150</v>
       </c>
@@ -2279,7 +2335,7 @@
         <v>175</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>226</v>
@@ -2291,7 +2347,7 @@
         <v>176</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>227</v>
@@ -2302,7 +2358,7 @@
         <v>177</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>199</v>
@@ -2313,7 +2369,7 @@
         <v>178</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>228</v>
@@ -2324,7 +2380,7 @@
         <v>179</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="4:5">
@@ -2332,7 +2388,7 @@
         <v>180</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="4:5">
@@ -2340,7 +2396,7 @@
         <v>181</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="4:5">
@@ -2348,7 +2404,7 @@
         <v>182</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="4:5">
@@ -2356,7 +2412,7 @@
         <v>183</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="4:5">
@@ -2364,39 +2420,39 @@
         <v>184</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="4:5">
       <c r="D22" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="E22" s="11" t="s">
-        <v>234</v>
+      <c r="E22" s="10" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="4:5">
       <c r="D23" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="E23" s="11" t="s">
-        <v>233</v>
+      <c r="E23" s="10" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="24" spans="4:5">
       <c r="D24" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>211</v>
+      <c r="E24" s="11" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="4:5">
       <c r="D25" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>212</v>
+      <c r="E25" s="11" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="4:5">
@@ -2404,7 +2460,7 @@
         <v>189</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="4:5">
@@ -2412,7 +2468,7 @@
         <v>193</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="4:5">
@@ -2420,12 +2476,20 @@
         <v>190</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="4:5">
       <c r="D29" s="10" t="s">
         <v>191</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" spans="4:5">
+      <c r="E30" s="10" t="s">
+        <v>215</v>
       </c>
     </row>
   </sheetData>
